--- a/servers/maze_main_server_dev/conf.d/data/maze_kongfu_extra_coin_v8【迷宫-武力值对应额外钱币】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_kongfu_extra_coin_v8【迷宫-武力值对应额外钱币】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48CF80C1-5A0B-41DD-99CF-76EC723B9364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FDE1C3-6F11-4F56-AE90-59BB25AEB6A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -103,6 +103,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>1:1_2:2_3:3_4:4_5:5_6:6_7:7_8:8_9:9_10:10_11:11_12:12_13:13_14:14_15:15_16:16_17:17_18:18_19:19_20:20_21:21_22:22_23:23_24:24_25:25_26:26_27:27_28:28_29:29_30:30_31:31_32:32_33:33_34:34_35:35_36:36_37:37_38:38_39:39_40:40_41:41_42:42_43:43_44:44_45:45_46:46_47:47_48:48_49:49_50:50_51:51_52:52_53:53_54:54_55:55_56:56_57:57_58:58_59:59_60:60_61:61_62:62_63:63_64:64_65:65_66:66_67:67_68:68_69:69_70:70_71:71_72:72_73:73_74:74_75:75_76:76_77:77_78:78_79:79_80:80_81:81_82:82_83:83_84:84_85:85_86:86_87:87_88:88_89:89_90:90_91:91_92:92_93:93_94:94_95:95_96:96_97:97_98:98_99:99_100:100_101:101_102:102_103:103_104:104_105:105_106:106_107:107_108:108_109:109_110:110_111:111_112:112_113:113_114:114_115:115_116:116_117:117_118:118_119:119_120:120_121:121_122:122_123:123_124:124_125:125_126:126_127:127_128:128_129:129_130:130_131:131_132:132_133:133_134:134_135:135_136:136_137:137_138:138_139:139_140:140_141:141_142:142_143:143_144:144_145:145_146:146_147:147_148:148_149:149_150:150_151:151_152:152_153:153_154:154_155:155_156:156_157:157_158:158_159:159_160:160</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>产出类型（1-银币 2-装备分 3-经验）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -125,9 +129,6 @@
   <si>
     <t>MAP&lt;INT:LONG&gt;_C_S</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:0_2:0_3:0_4:0_5:0_6:0_7:0_8:0_9:0_10:0_11:0_12:0_13:0_14:0_15:0_16:0_17:0_18:0_19:0_20:0_21:0_22:0_23:0_24:0_25:0_26:0_27:0_28:0_29:0_30:0_31:0_32:0_33:0_34:0_35:0_36:0_37:0_38:0_39:0_40:0_41:0_42:0_43:0_44:0_45:0_46:0_47:0_48:0_49:0_50:0_51:0_52:0_53:0_54:0_55:0_56:0_57:0_58:0_59:0_60:0_61:0_62:0_63:0_64:0_65:0_66:0_67:0_68:0_69:0_70:0_71:0_72:0_73:0_74:0_75:0_76:0_77:0_78:0_79:0_80:0_81:0_82:0_83:0_84:0_85:0_86:0_87:0_88:0_89:0_90:0_91:0_92:0_93:0_94:0_95:0_96:0_97:0_98:0_99:0_100:0_101:0_102:0_103:0_104:0_105:0_106:0_107:0_108:0_109:0_110:0_111:0_112:0_113:0_114:0_115:0_116:0_117:0_118:0_119:0_120:0_121:0_122:0_123:0_124:0_125:0_126:0_127:0_128:0_129:0_130:0_131:0_132:0_133:0_134:0_135:0_136:0_137:0_138:0_139:0_140:0_141:0_142:0_143:0_144:0_145:0_146:0_147:0_148:0_149:0_150:0_151:0_152:0_153:0_154:0_155:0_156:0_157:0_158:0_159:0_160:0</t>
   </si>
 </sst>
 </file>
@@ -491,16 +492,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -525,7 +526,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>6</v>
@@ -534,7 +535,7 @@
         <v>7</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -551,7 +552,7 @@
         <v>714</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -568,7 +569,7 @@
         <v>879</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -585,7 +586,7 @@
         <v>1319</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -602,7 +603,7 @@
         <v>1799</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -619,7 +620,7 @@
         <v>2199</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -636,7 +637,7 @@
         <v>3049</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -653,7 +654,7 @@
         <v>3999</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -670,7 +671,7 @@
         <v>4899</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -687,7 +688,7 @@
         <v>6099</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -704,7 +705,7 @@
         <v>7899</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -721,7 +722,7 @@
         <v>9649</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -738,7 +739,7 @@
         <v>13279</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -755,7 +756,7 @@
         <v>15999</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -772,7 +773,7 @@
         <v>22499</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -789,7 +790,7 @@
         <v>25999</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -806,7 +807,7 @@
         <v>39999</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -823,7 +824,7 @@
         <v>46999</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
@@ -840,7 +841,7 @@
         <v>53999</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
@@ -857,7 +858,7 @@
         <v>89999</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
@@ -874,7 +875,7 @@
         <v>107999</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
@@ -891,7 +892,7 @@
         <v>126999</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
@@ -908,7 +909,7 @@
         <v>193999</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
@@ -925,7 +926,7 @@
         <v>227999</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
@@ -942,7 +943,7 @@
         <v>261999</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
@@ -959,7 +960,7 @@
         <v>99999999</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
@@ -976,7 +977,7 @@
         <v>714</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
@@ -993,7 +994,7 @@
         <v>879</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
@@ -1010,7 +1011,7 @@
         <v>1319</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -1027,7 +1028,7 @@
         <v>1799</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
@@ -1044,7 +1045,7 @@
         <v>2199</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
@@ -1061,7 +1062,7 @@
         <v>3049</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
@@ -1078,7 +1079,7 @@
         <v>3999</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
@@ -1095,7 +1096,7 @@
         <v>4899</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
@@ -1112,7 +1113,7 @@
         <v>6099</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
@@ -1129,7 +1130,7 @@
         <v>7899</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
@@ -1146,7 +1147,7 @@
         <v>9649</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
@@ -1163,7 +1164,7 @@
         <v>13279</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
@@ -1180,7 +1181,7 @@
         <v>15999</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
@@ -1197,7 +1198,7 @@
         <v>22499</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
@@ -1214,7 +1215,7 @@
         <v>25999</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
@@ -1231,7 +1232,7 @@
         <v>39999</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
@@ -1248,7 +1249,7 @@
         <v>46999</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
@@ -1265,7 +1266,7 @@
         <v>53999</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
@@ -1282,7 +1283,7 @@
         <v>89999</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
@@ -1299,7 +1300,7 @@
         <v>107999</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
@@ -1316,7 +1317,7 @@
         <v>126999</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
@@ -1333,7 +1334,7 @@
         <v>193999</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
@@ -1350,7 +1351,7 @@
         <v>227999</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
@@ -1367,7 +1368,7 @@
         <v>261999</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
@@ -1384,7 +1385,7 @@
         <v>99999999</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
@@ -1401,7 +1402,7 @@
         <v>714</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
@@ -1418,7 +1419,7 @@
         <v>879</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
@@ -1435,7 +1436,7 @@
         <v>1319</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
@@ -1452,7 +1453,7 @@
         <v>1799</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
@@ -1469,7 +1470,7 @@
         <v>2199</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
@@ -1486,7 +1487,7 @@
         <v>3049</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
@@ -1503,7 +1504,7 @@
         <v>3999</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
@@ -1520,7 +1521,7 @@
         <v>4899</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
@@ -1537,7 +1538,7 @@
         <v>6099</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
@@ -1554,7 +1555,7 @@
         <v>7899</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
@@ -1571,7 +1572,7 @@
         <v>9649</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
@@ -1588,7 +1589,7 @@
         <v>13279</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
@@ -1605,7 +1606,7 @@
         <v>15999</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
@@ -1622,7 +1623,7 @@
         <v>22499</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
@@ -1639,7 +1640,7 @@
         <v>25999</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
@@ -1656,7 +1657,7 @@
         <v>39999</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
@@ -1673,7 +1674,7 @@
         <v>46999</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
@@ -1690,7 +1691,7 @@
         <v>53999</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
@@ -1707,7 +1708,7 @@
         <v>89999</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
@@ -1724,7 +1725,7 @@
         <v>107999</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
@@ -1741,7 +1742,7 @@
         <v>126999</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
@@ -1758,7 +1759,7 @@
         <v>193999</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
@@ -1775,7 +1776,7 @@
         <v>227999</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
@@ -1792,7 +1793,7 @@
         <v>261999</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
@@ -1809,7 +1810,7 @@
         <v>99999999</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server_dev/conf.d/data/maze_kongfu_extra_coin_v8【迷宫-武力值对应额外钱币】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_kongfu_extra_coin_v8【迷宫-武力值对应额外钱币】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FDE1C3-6F11-4F56-AE90-59BB25AEB6A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48CF80C1-5A0B-41DD-99CF-76EC723B9364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -103,10 +103,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:1_2:2_3:3_4:4_5:5_6:6_7:7_8:8_9:9_10:10_11:11_12:12_13:13_14:14_15:15_16:16_17:17_18:18_19:19_20:20_21:21_22:22_23:23_24:24_25:25_26:26_27:27_28:28_29:29_30:30_31:31_32:32_33:33_34:34_35:35_36:36_37:37_38:38_39:39_40:40_41:41_42:42_43:43_44:44_45:45_46:46_47:47_48:48_49:49_50:50_51:51_52:52_53:53_54:54_55:55_56:56_57:57_58:58_59:59_60:60_61:61_62:62_63:63_64:64_65:65_66:66_67:67_68:68_69:69_70:70_71:71_72:72_73:73_74:74_75:75_76:76_77:77_78:78_79:79_80:80_81:81_82:82_83:83_84:84_85:85_86:86_87:87_88:88_89:89_90:90_91:91_92:92_93:93_94:94_95:95_96:96_97:97_98:98_99:99_100:100_101:101_102:102_103:103_104:104_105:105_106:106_107:107_108:108_109:109_110:110_111:111_112:112_113:113_114:114_115:115_116:116_117:117_118:118_119:119_120:120_121:121_122:122_123:123_124:124_125:125_126:126_127:127_128:128_129:129_130:130_131:131_132:132_133:133_134:134_135:135_136:136_137:137_138:138_139:139_140:140_141:141_142:142_143:143_144:144_145:145_146:146_147:147_148:148_149:149_150:150_151:151_152:152_153:153_154:154_155:155_156:156_157:157_158:158_159:159_160:160</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>产出类型（1-银币 2-装备分 3-经验）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -129,6 +125,9 @@
   <si>
     <t>MAP&lt;INT:LONG&gt;_C_S</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:0_2:0_3:0_4:0_5:0_6:0_7:0_8:0_9:0_10:0_11:0_12:0_13:0_14:0_15:0_16:0_17:0_18:0_19:0_20:0_21:0_22:0_23:0_24:0_25:0_26:0_27:0_28:0_29:0_30:0_31:0_32:0_33:0_34:0_35:0_36:0_37:0_38:0_39:0_40:0_41:0_42:0_43:0_44:0_45:0_46:0_47:0_48:0_49:0_50:0_51:0_52:0_53:0_54:0_55:0_56:0_57:0_58:0_59:0_60:0_61:0_62:0_63:0_64:0_65:0_66:0_67:0_68:0_69:0_70:0_71:0_72:0_73:0_74:0_75:0_76:0_77:0_78:0_79:0_80:0_81:0_82:0_83:0_84:0_85:0_86:0_87:0_88:0_89:0_90:0_91:0_92:0_93:0_94:0_95:0_96:0_97:0_98:0_99:0_100:0_101:0_102:0_103:0_104:0_105:0_106:0_107:0_108:0_109:0_110:0_111:0_112:0_113:0_114:0_115:0_116:0_117:0_118:0_119:0_120:0_121:0_122:0_123:0_124:0_125:0_126:0_127:0_128:0_129:0_130:0_131:0_132:0_133:0_134:0_135:0_136:0_137:0_138:0_139:0_140:0_141:0_142:0_143:0_144:0_145:0_146:0_147:0_148:0_149:0_150:0_151:0_152:0_153:0_154:0_155:0_156:0_157:0_158:0_159:0_160:0</t>
   </si>
 </sst>
 </file>
@@ -492,16 +491,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -526,7 +525,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>6</v>
@@ -535,7 +534,7 @@
         <v>7</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -552,7 +551,7 @@
         <v>714</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -569,7 +568,7 @@
         <v>879</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -586,7 +585,7 @@
         <v>1319</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -603,7 +602,7 @@
         <v>1799</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -620,7 +619,7 @@
         <v>2199</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -637,7 +636,7 @@
         <v>3049</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -654,7 +653,7 @@
         <v>3999</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -671,7 +670,7 @@
         <v>4899</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -688,7 +687,7 @@
         <v>6099</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -705,7 +704,7 @@
         <v>7899</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -722,7 +721,7 @@
         <v>9649</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -739,7 +738,7 @@
         <v>13279</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -756,7 +755,7 @@
         <v>15999</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -773,7 +772,7 @@
         <v>22499</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -790,7 +789,7 @@
         <v>25999</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -807,7 +806,7 @@
         <v>39999</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -824,7 +823,7 @@
         <v>46999</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
@@ -841,7 +840,7 @@
         <v>53999</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
@@ -858,7 +857,7 @@
         <v>89999</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
@@ -875,7 +874,7 @@
         <v>107999</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
@@ -892,7 +891,7 @@
         <v>126999</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
@@ -909,7 +908,7 @@
         <v>193999</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
@@ -926,7 +925,7 @@
         <v>227999</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
@@ -943,7 +942,7 @@
         <v>261999</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
@@ -960,7 +959,7 @@
         <v>99999999</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
@@ -977,7 +976,7 @@
         <v>714</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
@@ -994,7 +993,7 @@
         <v>879</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
@@ -1011,7 +1010,7 @@
         <v>1319</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -1028,7 +1027,7 @@
         <v>1799</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
@@ -1045,7 +1044,7 @@
         <v>2199</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
@@ -1062,7 +1061,7 @@
         <v>3049</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
@@ -1079,7 +1078,7 @@
         <v>3999</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
@@ -1096,7 +1095,7 @@
         <v>4899</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
@@ -1113,7 +1112,7 @@
         <v>6099</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
@@ -1130,7 +1129,7 @@
         <v>7899</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
@@ -1147,7 +1146,7 @@
         <v>9649</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
@@ -1164,7 +1163,7 @@
         <v>13279</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
@@ -1181,7 +1180,7 @@
         <v>15999</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
@@ -1198,7 +1197,7 @@
         <v>22499</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
@@ -1215,7 +1214,7 @@
         <v>25999</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
@@ -1232,7 +1231,7 @@
         <v>39999</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
@@ -1249,7 +1248,7 @@
         <v>46999</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
@@ -1266,7 +1265,7 @@
         <v>53999</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
@@ -1283,7 +1282,7 @@
         <v>89999</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
@@ -1300,7 +1299,7 @@
         <v>107999</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
@@ -1317,7 +1316,7 @@
         <v>126999</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
@@ -1334,7 +1333,7 @@
         <v>193999</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
@@ -1351,7 +1350,7 @@
         <v>227999</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
@@ -1368,7 +1367,7 @@
         <v>261999</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
@@ -1385,7 +1384,7 @@
         <v>99999999</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
@@ -1402,7 +1401,7 @@
         <v>714</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
@@ -1419,7 +1418,7 @@
         <v>879</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
@@ -1436,7 +1435,7 @@
         <v>1319</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
@@ -1453,7 +1452,7 @@
         <v>1799</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
@@ -1470,7 +1469,7 @@
         <v>2199</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
@@ -1487,7 +1486,7 @@
         <v>3049</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
@@ -1504,7 +1503,7 @@
         <v>3999</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
@@ -1521,7 +1520,7 @@
         <v>4899</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
@@ -1538,7 +1537,7 @@
         <v>6099</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
@@ -1555,7 +1554,7 @@
         <v>7899</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
@@ -1572,7 +1571,7 @@
         <v>9649</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
@@ -1589,7 +1588,7 @@
         <v>13279</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
@@ -1606,7 +1605,7 @@
         <v>15999</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
@@ -1623,7 +1622,7 @@
         <v>22499</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
@@ -1640,7 +1639,7 @@
         <v>25999</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
@@ -1657,7 +1656,7 @@
         <v>39999</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
@@ -1674,7 +1673,7 @@
         <v>46999</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
@@ -1691,7 +1690,7 @@
         <v>53999</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
@@ -1708,7 +1707,7 @@
         <v>89999</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
@@ -1725,7 +1724,7 @@
         <v>107999</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
@@ -1742,7 +1741,7 @@
         <v>126999</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
@@ -1759,7 +1758,7 @@
         <v>193999</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
@@ -1776,7 +1775,7 @@
         <v>227999</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
@@ -1793,7 +1792,7 @@
         <v>261999</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
@@ -1810,7 +1809,7 @@
         <v>99999999</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
